--- a/Kwartaalrapportage/VISMA/Q1 2026 Mobility.xlsx
+++ b/Kwartaalrapportage/VISMA/Q1 2026 Mobility.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tgf-my.sharepoint.com/personal/tom_meijer_theglobalfund_org/Documents/Documents/Temp/Blueplates/Rapportage/Q1 2026/VISMA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="80" documentId="11_1793008D02D80C5747D2C04F36DF63C4FFAA5679" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{71ABA5EA-3112-FA4E-A654-928A84740AFC}"/>
+  <xr:revisionPtr revIDLastSave="84" documentId="11_1793008D02D80C5747D2C04F36DF63C4FFAA5679" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5030A43B-8674-8C49-B636-C9DA53C36DDA}"/>
   <bookViews>
     <workbookView xWindow="-38400" yWindow="600" windowWidth="38400" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="166">
   <si>
     <t>Organisatie:</t>
   </si>
@@ -417,9 +417,6 @@
   </si>
   <si>
     <t>Overige huisvestingsKosten</t>
-  </si>
-  <si>
-    <t>441300</t>
   </si>
   <si>
     <t>Lease- en huurKosten auto</t>
@@ -1311,16 +1308,16 @@
         <v>15</v>
       </c>
       <c r="H6" s="14" t="s">
+        <v>162</v>
+      </c>
+      <c r="I6" s="14" t="s">
         <v>163</v>
       </c>
-      <c r="I6" s="14" t="s">
+      <c r="J6" s="14" t="s">
         <v>164</v>
       </c>
-      <c r="J6" s="14" t="s">
+      <c r="K6" s="14" t="s">
         <v>165</v>
-      </c>
-      <c r="K6" s="14" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="7" spans="1:15" ht="12" x14ac:dyDescent="0.15">
@@ -1576,8 +1573,7 @@
         <v>114309.13</v>
       </c>
       <c r="K13" s="16">
-        <f t="shared" si="0"/>
-        <v>489767.94999999995</v>
+        <v>0</v>
       </c>
       <c r="L13" s="16"/>
       <c r="M13" s="16"/>
@@ -2048,8 +2044,7 @@
         <v>199382.51</v>
       </c>
       <c r="K26" s="16">
-        <f t="shared" si="0"/>
-        <v>-623388.77</v>
+        <v>-133620.82000000007</v>
       </c>
       <c r="M26" s="16"/>
     </row>
@@ -3171,14 +3166,14 @@
       </c>
     </row>
     <row r="58" spans="1:11" ht="12" x14ac:dyDescent="0.15">
-      <c r="A58" s="5" t="s">
-        <v>128</v>
+      <c r="A58" s="5">
+        <v>441300</v>
       </c>
       <c r="B58" s="5" t="s">
         <v>125</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D58" s="11">
         <v>0</v>
@@ -3208,13 +3203,13 @@
     </row>
     <row r="59" spans="1:11" ht="12" x14ac:dyDescent="0.15">
       <c r="A59" s="5" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B59" s="5" t="s">
         <v>125</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D59" s="11">
         <v>0</v>
@@ -3244,13 +3239,13 @@
     </row>
     <row r="60" spans="1:11" ht="12" x14ac:dyDescent="0.15">
       <c r="A60" s="5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B60" s="5" t="s">
         <v>125</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D60" s="11">
         <v>0</v>
@@ -3280,13 +3275,13 @@
     </row>
     <row r="61" spans="1:11" ht="12" x14ac:dyDescent="0.15">
       <c r="A61" s="5" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B61" s="5" t="s">
         <v>125</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D61" s="11">
         <v>0</v>
@@ -3316,13 +3311,13 @@
     </row>
     <row r="62" spans="1:11" ht="12" x14ac:dyDescent="0.15">
       <c r="A62" s="5" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B62" s="5" t="s">
         <v>125</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D62" s="11">
         <v>0</v>
@@ -3352,13 +3347,13 @@
     </row>
     <row r="63" spans="1:11" ht="12" x14ac:dyDescent="0.15">
       <c r="A63" s="5" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B63" s="5" t="s">
         <v>125</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D63" s="11">
         <v>0</v>
@@ -3388,13 +3383,13 @@
     </row>
     <row r="64" spans="1:11" ht="12" x14ac:dyDescent="0.15">
       <c r="A64" s="5" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B64" s="5" t="s">
         <v>125</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D64" s="11">
         <v>0</v>
@@ -3424,13 +3419,13 @@
     </row>
     <row r="65" spans="1:11" ht="12" x14ac:dyDescent="0.15">
       <c r="A65" s="5" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B65" s="5" t="s">
         <v>125</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D65" s="11">
         <v>0</v>
@@ -3460,13 +3455,13 @@
     </row>
     <row r="66" spans="1:11" ht="12" x14ac:dyDescent="0.15">
       <c r="A66" s="5" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B66" s="5" t="s">
         <v>125</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D66" s="11">
         <v>0</v>
@@ -3496,13 +3491,13 @@
     </row>
     <row r="67" spans="1:11" ht="12" x14ac:dyDescent="0.15">
       <c r="A67" s="5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B67" s="5" t="s">
         <v>125</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D67" s="11">
         <v>0</v>
@@ -3532,13 +3527,13 @@
     </row>
     <row r="68" spans="1:11" ht="12" x14ac:dyDescent="0.15">
       <c r="A68" s="5" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B68" s="5" t="s">
         <v>125</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D68" s="11">
         <v>0</v>
@@ -3568,13 +3563,13 @@
     </row>
     <row r="69" spans="1:11" ht="12" x14ac:dyDescent="0.15">
       <c r="A69" s="5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B69" s="5" t="s">
         <v>125</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D69" s="11">
         <v>0</v>
@@ -3604,13 +3599,13 @@
     </row>
     <row r="70" spans="1:11" ht="12" x14ac:dyDescent="0.15">
       <c r="A70" s="5" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B70" s="5" t="s">
         <v>125</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D70" s="11">
         <v>0</v>
@@ -3640,13 +3635,13 @@
     </row>
     <row r="71" spans="1:11" ht="12" x14ac:dyDescent="0.15">
       <c r="A71" s="5" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B71" s="5" t="s">
         <v>125</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D71" s="11">
         <v>0</v>
@@ -3676,13 +3671,13 @@
     </row>
     <row r="72" spans="1:11" ht="12" x14ac:dyDescent="0.15">
       <c r="A72" s="5" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B72" s="5" t="s">
         <v>125</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D72" s="11">
         <v>0</v>
@@ -3712,13 +3707,13 @@
     </row>
     <row r="73" spans="1:11" ht="12" x14ac:dyDescent="0.15">
       <c r="A73" s="5" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B73" s="5" t="s">
         <v>125</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D73" s="11">
         <v>0</v>
@@ -3748,13 +3743,13 @@
     </row>
     <row r="74" spans="1:11" ht="12" x14ac:dyDescent="0.15">
       <c r="A74" s="5" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B74" s="5" t="s">
         <v>125</v>
       </c>
       <c r="C74" s="5" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D74" s="11">
         <v>0</v>
@@ -3786,7 +3781,7 @@
       <c r="A75" s="4"/>
       <c r="B75" s="4"/>
       <c r="C75" s="12" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D75" s="13">
         <v>-5.4133142413093102E-11</v>
